--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076204</v>
+        <v>124076185</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -733,7 +729,7 @@
         <v>6377778</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076569</v>
+        <v>124076253</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579183</v>
+        <v>579177</v>
       </c>
       <c r="R3" t="n">
-        <v>6377804</v>
+        <v>6377716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,14 +890,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076369</v>
+        <v>124076142</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -933,11 +930,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -952,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579244</v>
+        <v>579194</v>
       </c>
       <c r="R4" t="n">
-        <v>6377641</v>
+        <v>6377795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076142</v>
+        <v>124076548</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1063,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579194</v>
+        <v>579195</v>
       </c>
       <c r="R5" t="n">
-        <v>6377795</v>
+        <v>6377792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076548</v>
+        <v>124076569</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1174,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579195</v>
+        <v>579183</v>
       </c>
       <c r="R6" t="n">
-        <v>6377792</v>
+        <v>6377804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076185</v>
+        <v>124076382</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1270,7 +1263,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1281,14 +1278,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579183</v>
+        <v>579252</v>
       </c>
       <c r="R7" t="n">
-        <v>6377778</v>
+        <v>6377628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076253</v>
+        <v>124076369</v>
       </c>
       <c r="B8" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,28 +1357,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1396,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579177</v>
+        <v>579244</v>
       </c>
       <c r="R8" t="n">
-        <v>6377716</v>
+        <v>6377641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,14 +1453,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076589</v>
+        <v>124076560</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1503,14 +1504,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579184</v>
+        <v>579182</v>
       </c>
       <c r="R9" t="n">
-        <v>6377801</v>
+        <v>6377811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076382</v>
+        <v>124076204</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,53 +1583,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579252</v>
+        <v>579183</v>
       </c>
       <c r="R10" t="n">
-        <v>6377628</v>
+        <v>6377778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1667,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076560</v>
+        <v>124076589</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1729,14 +1729,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579182</v>
+        <v>579184</v>
       </c>
       <c r="R11" t="n">
-        <v>6377811</v>
+        <v>6377801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076185</v>
+        <v>124076253</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579183</v>
+        <v>579177</v>
       </c>
       <c r="R2" t="n">
-        <v>6377778</v>
+        <v>6377716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076253</v>
+        <v>124076382</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,28 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -830,14 +834,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579177</v>
+        <v>579252</v>
       </c>
       <c r="R3" t="n">
-        <v>6377716</v>
+        <v>6377628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,14 +894,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076142</v>
+        <v>124076589</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,14 +945,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579194</v>
+        <v>579184</v>
       </c>
       <c r="R4" t="n">
-        <v>6377795</v>
+        <v>6377801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076548</v>
+        <v>124076204</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,49 +1024,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579195</v>
+        <v>579183</v>
       </c>
       <c r="R5" t="n">
-        <v>6377792</v>
+        <v>6377778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1108,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076382</v>
+        <v>124076185</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1263,11 +1270,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1278,14 +1281,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579252</v>
+        <v>579183</v>
       </c>
       <c r="R7" t="n">
-        <v>6377628</v>
+        <v>6377778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076369</v>
+        <v>124076548</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1378,11 +1381,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579244</v>
+        <v>579195</v>
       </c>
       <c r="R8" t="n">
-        <v>6377641</v>
+        <v>6377792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076560</v>
+        <v>124076142</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1508,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579182</v>
+        <v>579194</v>
       </c>
       <c r="R9" t="n">
-        <v>6377811</v>
+        <v>6377795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076204</v>
+        <v>124076369</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,53 +1582,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579183</v>
+        <v>579244</v>
       </c>
       <c r="R10" t="n">
-        <v>6377778</v>
+        <v>6377641</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,6 +1666,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076589</v>
+        <v>124076560</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1729,14 +1729,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579184</v>
+        <v>579182</v>
       </c>
       <c r="R11" t="n">
-        <v>6377801</v>
+        <v>6377811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076548</v>
+        <v>124076185</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579195</v>
+        <v>579183</v>
       </c>
       <c r="R2" t="n">
-        <v>6377792</v>
+        <v>6377778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076142</v>
+        <v>124076369</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,7 +819,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579194</v>
+        <v>579244</v>
       </c>
       <c r="R3" t="n">
-        <v>6377795</v>
+        <v>6377641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076589</v>
+        <v>124076382</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,7 +1048,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1055,14 +1063,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579184</v>
+        <v>579252</v>
       </c>
       <c r="R5" t="n">
-        <v>6377801</v>
+        <v>6377628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1226,14 +1234,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076369</v>
+        <v>124076589</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,11 +1274,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1281,14 +1285,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579244</v>
+        <v>579184</v>
       </c>
       <c r="R7" t="n">
-        <v>6377641</v>
+        <v>6377801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,14 +1345,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076382</v>
+        <v>124076548</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1381,11 +1385,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1396,14 +1396,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579252</v>
+        <v>579195</v>
       </c>
       <c r="R8" t="n">
-        <v>6377628</v>
+        <v>6377792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076185</v>
+        <v>124076560</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1618,14 +1618,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579183</v>
+        <v>579182</v>
       </c>
       <c r="R10" t="n">
-        <v>6377778</v>
+        <v>6377811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,14 +1678,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076560</v>
+        <v>124076142</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579182</v>
+        <v>579194</v>
       </c>
       <c r="R11" t="n">
-        <v>6377811</v>
+        <v>6377795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076185</v>
+        <v>124076204</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -729,7 +733,7 @@
         <v>6377778</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076369</v>
+        <v>124076589</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,11 +822,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -834,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579244</v>
+        <v>579184</v>
       </c>
       <c r="R3" t="n">
-        <v>6377641</v>
+        <v>6377801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076204</v>
+        <v>124076569</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,53 +912,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>579183</v>
       </c>
       <c r="R4" t="n">
-        <v>6377778</v>
+        <v>6377804</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076382</v>
+        <v>124076560</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1048,11 +1044,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1063,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579252</v>
+        <v>579182</v>
       </c>
       <c r="R5" t="n">
-        <v>6377628</v>
+        <v>6377811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076569</v>
+        <v>124076382</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1163,7 +1155,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1174,14 +1170,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579183</v>
+        <v>579252</v>
       </c>
       <c r="R6" t="n">
-        <v>6377804</v>
+        <v>6377628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,14 +1230,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076589</v>
+        <v>124076142</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,14 +1281,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579184</v>
+        <v>579194</v>
       </c>
       <c r="R7" t="n">
-        <v>6377801</v>
+        <v>6377795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1456,17 +1452,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076253</v>
+        <v>124076185</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,14 +1503,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579177</v>
+        <v>579183</v>
       </c>
       <c r="R9" t="n">
-        <v>6377716</v>
+        <v>6377778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,14 +1563,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076560</v>
+        <v>124076369</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1607,7 +1603,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579182</v>
+        <v>579244</v>
       </c>
       <c r="R10" t="n">
-        <v>6377811</v>
+        <v>6377641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,17 +1678,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076142</v>
+        <v>124076253</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,25 +1697,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579194</v>
+        <v>579177</v>
       </c>
       <c r="R11" t="n">
-        <v>6377795</v>
+        <v>6377716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076204</v>
+        <v>124076569</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>579183</v>
       </c>
       <c r="R2" t="n">
-        <v>6377778</v>
+        <v>6377804</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076589</v>
+        <v>124076548</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -833,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579184</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6377801</v>
+        <v>6377792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076569</v>
+        <v>124076369</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -933,7 +930,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579183</v>
+        <v>579244</v>
       </c>
       <c r="R4" t="n">
-        <v>6377804</v>
+        <v>6377641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076560</v>
+        <v>124076382</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,7 +1045,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1055,14 +1060,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579182</v>
+        <v>579252</v>
       </c>
       <c r="R5" t="n">
-        <v>6377811</v>
+        <v>6377628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076382</v>
+        <v>124076253</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,32 +1139,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1170,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579252</v>
+        <v>579177</v>
       </c>
       <c r="R6" t="n">
-        <v>6377628</v>
+        <v>6377716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,14 +1231,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076142</v>
+        <v>124076185</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1281,14 +1282,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579194</v>
+        <v>579183</v>
       </c>
       <c r="R7" t="n">
-        <v>6377795</v>
+        <v>6377778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076548</v>
+        <v>124076589</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1392,14 +1393,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579195</v>
+        <v>579184</v>
       </c>
       <c r="R8" t="n">
-        <v>6377792</v>
+        <v>6377801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076185</v>
+        <v>124076142</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1503,14 +1504,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579183</v>
+        <v>579194</v>
       </c>
       <c r="R9" t="n">
-        <v>6377778</v>
+        <v>6377795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076369</v>
+        <v>124076560</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1603,11 +1604,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1622,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579244</v>
+        <v>579182</v>
       </c>
       <c r="R10" t="n">
-        <v>6377641</v>
+        <v>6377811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076253</v>
+        <v>124076204</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,49 +1694,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579177</v>
+        <v>579183</v>
       </c>
       <c r="R11" t="n">
-        <v>6377716</v>
+        <v>6377778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1778,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076569</v>
+        <v>124076204</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>579183</v>
       </c>
       <c r="R2" t="n">
-        <v>6377804</v>
+        <v>6377778</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076548</v>
+        <v>124076253</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579177</v>
       </c>
       <c r="R3" t="n">
-        <v>6377792</v>
+        <v>6377716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,14 +893,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076369</v>
+        <v>124076382</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,14 +948,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579244</v>
+        <v>579252</v>
       </c>
       <c r="R4" t="n">
-        <v>6377641</v>
+        <v>6377628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076382</v>
+        <v>124076560</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1045,11 +1048,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1060,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579252</v>
+        <v>579182</v>
       </c>
       <c r="R5" t="n">
-        <v>6377628</v>
+        <v>6377811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076253</v>
+        <v>124076589</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,14 +1170,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579177</v>
+        <v>579184</v>
       </c>
       <c r="R6" t="n">
-        <v>6377716</v>
+        <v>6377801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,14 +1230,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076185</v>
+        <v>124076142</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1282,14 +1281,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579183</v>
+        <v>579194</v>
       </c>
       <c r="R7" t="n">
-        <v>6377778</v>
+        <v>6377795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076589</v>
+        <v>124076185</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1393,14 +1392,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579184</v>
+        <v>579183</v>
       </c>
       <c r="R8" t="n">
-        <v>6377801</v>
+        <v>6377778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076142</v>
+        <v>124076569</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1508,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579194</v>
+        <v>579183</v>
       </c>
       <c r="R9" t="n">
-        <v>6377795</v>
+        <v>6377804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1570,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076560</v>
+        <v>124076548</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1619,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579182</v>
+        <v>579195</v>
       </c>
       <c r="R10" t="n">
-        <v>6377811</v>
+        <v>6377792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076204</v>
+        <v>124076369</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,53 +1693,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579183</v>
+        <v>579244</v>
       </c>
       <c r="R11" t="n">
-        <v>6377778</v>
+        <v>6377641</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,6 +1777,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076204</v>
+        <v>124076253</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579183</v>
+        <v>579177</v>
       </c>
       <c r="R2" t="n">
-        <v>6377778</v>
+        <v>6377716</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076253</v>
+        <v>124076204</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,49 +798,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579177</v>
+        <v>579183</v>
       </c>
       <c r="R3" t="n">
-        <v>6377716</v>
+        <v>6377778</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,14 +893,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076382</v>
+        <v>124076369</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -948,14 +948,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579252</v>
+        <v>579244</v>
       </c>
       <c r="R4" t="n">
-        <v>6377628</v>
+        <v>6377641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076560</v>
+        <v>124076185</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1059,14 +1059,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579182</v>
+        <v>579183</v>
       </c>
       <c r="R5" t="n">
-        <v>6377811</v>
+        <v>6377778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076589</v>
+        <v>124076382</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1159,7 +1159,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1170,14 +1174,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579184</v>
+        <v>579252</v>
       </c>
       <c r="R6" t="n">
-        <v>6377801</v>
+        <v>6377628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076142</v>
+        <v>124076569</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579194</v>
+        <v>579183</v>
       </c>
       <c r="R7" t="n">
-        <v>6377795</v>
+        <v>6377804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076185</v>
+        <v>124076560</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1392,14 +1396,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579183</v>
+        <v>579182</v>
       </c>
       <c r="R8" t="n">
-        <v>6377778</v>
+        <v>6377811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076569</v>
+        <v>124076548</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1507,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579183</v>
+        <v>579195</v>
       </c>
       <c r="R9" t="n">
-        <v>6377804</v>
+        <v>6377792</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076548</v>
+        <v>124076142</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1618,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579195</v>
+        <v>579194</v>
       </c>
       <c r="R10" t="n">
-        <v>6377792</v>
+        <v>6377795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076369</v>
+        <v>124076589</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1714,11 +1718,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1729,14 +1729,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579244</v>
+        <v>579184</v>
       </c>
       <c r="R11" t="n">
-        <v>6377641</v>
+        <v>6377801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076253</v>
+        <v>124076560</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579177</v>
+        <v>579182</v>
       </c>
       <c r="R2" t="n">
-        <v>6377716</v>
+        <v>6377811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076204</v>
+        <v>124076369</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,53 +798,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579183</v>
+        <v>579244</v>
       </c>
       <c r="R3" t="n">
-        <v>6377778</v>
+        <v>6377641</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076369</v>
+        <v>124076569</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -933,11 +934,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -952,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579244</v>
+        <v>579183</v>
       </c>
       <c r="R4" t="n">
-        <v>6377641</v>
+        <v>6377804</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076185</v>
+        <v>124076382</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1048,7 +1045,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1059,14 +1060,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579183</v>
+        <v>579252</v>
       </c>
       <c r="R5" t="n">
-        <v>6377778</v>
+        <v>6377628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076382</v>
+        <v>124076253</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,32 +1139,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1174,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579252</v>
+        <v>579177</v>
       </c>
       <c r="R6" t="n">
-        <v>6377628</v>
+        <v>6377716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,14 +1231,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076569</v>
+        <v>124076589</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,14 +1282,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579183</v>
+        <v>579184</v>
       </c>
       <c r="R7" t="n">
-        <v>6377804</v>
+        <v>6377801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076560</v>
+        <v>124076142</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579182</v>
+        <v>579194</v>
       </c>
       <c r="R8" t="n">
-        <v>6377811</v>
+        <v>6377795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1574,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076142</v>
+        <v>124076204</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,49 +1583,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579194</v>
+        <v>579183</v>
       </c>
       <c r="R10" t="n">
-        <v>6377795</v>
+        <v>6377778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1667,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076589</v>
+        <v>124076185</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1729,14 +1729,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579184</v>
+        <v>579183</v>
       </c>
       <c r="R11" t="n">
-        <v>6377801</v>
+        <v>6377778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 13956-2025 artfynd.xlsx
+++ b/artfynd/A 13956-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076560</v>
+        <v>124076569</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579182</v>
+        <v>579183</v>
       </c>
       <c r="R2" t="n">
-        <v>6377811</v>
+        <v>6377804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076369</v>
+        <v>124076589</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,11 +819,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -834,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A  13956, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579244</v>
+        <v>579184</v>
       </c>
       <c r="R3" t="n">
-        <v>6377641</v>
+        <v>6377801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124076569</v>
+        <v>124076204</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,49 +909,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>579183</v>
       </c>
       <c r="R4" t="n">
-        <v>6377804</v>
+        <v>6377778</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124076382</v>
+        <v>124076548</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1045,11 +1044,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1060,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579252</v>
+        <v>579195</v>
       </c>
       <c r="R5" t="n">
-        <v>6377628</v>
+        <v>6377792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124076253</v>
+        <v>124076142</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579177</v>
+        <v>579194</v>
       </c>
       <c r="R6" t="n">
-        <v>6377716</v>
+        <v>6377795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,14 +1226,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124076589</v>
+        <v>124076560</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1282,14 +1277,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  13956, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579184</v>
+        <v>579182</v>
       </c>
       <c r="R7" t="n">
-        <v>6377801</v>
+        <v>6377811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124076142</v>
+        <v>124076369</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1382,7 +1377,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579194</v>
+        <v>579244</v>
       </c>
       <c r="R8" t="n">
-        <v>6377795</v>
+        <v>6377641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124076548</v>
+        <v>124076185</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1504,14 +1503,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 13956, Gissebo, Sm</t>
+          <t>A 13596, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579195</v>
+        <v>579183</v>
       </c>
       <c r="R9" t="n">
-        <v>6377792</v>
+        <v>6377778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124076204</v>
+        <v>124076253</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,53 +1582,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Gissebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579183</v>
+        <v>579177</v>
       </c>
       <c r="R10" t="n">
-        <v>6377778</v>
+        <v>6377716</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,6 +1662,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1678,14 +1674,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124076185</v>
+        <v>124076382</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1718,7 +1714,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1729,14 +1729,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 13596, Gissebo, Sm</t>
+          <t>A 13956, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579183</v>
+        <v>579252</v>
       </c>
       <c r="R11" t="n">
-        <v>6377778</v>
+        <v>6377628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
